--- a/tables/datas/#ServerConfig-区服配置表.xlsx
+++ b/tables/datas/#ServerConfig-区服配置表.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,69 +503,83 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>##</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>区服ID</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>区服名称</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>网关地址</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>网关端口</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>区服状态</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>是否新服</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>是否推荐</t>
-        </is>
-      </c>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="B4" t="n">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>区服ID</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>区服名称</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>网关地址</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>网关端口</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>区服状态</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>是否新服</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>是否推荐</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>测试服1</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>127.0.0.1</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E5" t="n">
         <v>8001</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F5" t="n">
         <v>1</v>
       </c>
-      <c r="G4" t="b">
+      <c r="G5" t="b">
         <v>0</v>
       </c>
-      <c r="H4" t="b">
+      <c r="H5" t="b">
         <v>1</v>
       </c>
     </row>
